--- a/data/trans_dic/P2A_fisi_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_fisi_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física</t>
+          <t>Hogares con personas con limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,35</t>
+          <t>2,05; 5,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 7,86</t>
+          <t>2,87; 8,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,16</t>
+          <t>2,0; 5,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,85; 12,16</t>
+          <t>6,87; 12,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,93</t>
+          <t>1,79; 5,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,56; 9,17</t>
+          <t>3,46; 9,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 7,62</t>
+          <t>2,59; 7,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,21; 7,97</t>
+          <t>4,46; 8,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,76</t>
+          <t>2,18; 4,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 7,3</t>
+          <t>3,53; 7,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 5,9</t>
+          <t>2,8; 5,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,07; 9,52</t>
+          <t>6,09; 9,41</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,07</t>
+          <t>1,33; 5,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,35; 8,07</t>
+          <t>3,59; 8,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,67; 6,99</t>
+          <t>2,6; 6,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,91; 9,83</t>
+          <t>4,81; 9,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,57; 7,07</t>
+          <t>2,28; 6,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,87; 9,43</t>
+          <t>3,63; 9,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 5,91</t>
+          <t>1,54; 5,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,61; 8,68</t>
+          <t>4,77; 8,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 5,16</t>
+          <t>2,32; 5,36</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,14; 7,81</t>
+          <t>4,09; 7,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,71</t>
+          <t>2,48; 5,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,35; 8,58</t>
+          <t>5,39; 8,7</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,12; 7,97</t>
+          <t>4,04; 8,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,06; 10,78</t>
+          <t>6,16; 11,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,45; 8,94</t>
+          <t>4,24; 8,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 13,71</t>
+          <t>3,02; 13,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,48; 13,65</t>
+          <t>4,48; 13,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,77; 12,74</t>
+          <t>5,68; 13,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,34; 14,65</t>
+          <t>4,35; 14,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,12; 16,9</t>
+          <t>8,12; 17,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,86; 8,48</t>
+          <t>4,66; 8,49</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,73; 10,8</t>
+          <t>6,73; 10,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,05; 8,99</t>
+          <t>5,05; 9,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,52; 13,21</t>
+          <t>3,48; 13,04</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,04; 7,89</t>
+          <t>5,07; 7,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,42; 11,23</t>
+          <t>7,54; 11,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,94; 8,2</t>
+          <t>4,88; 7,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,44; 14,58</t>
+          <t>10,36; 14,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,76; 8,95</t>
+          <t>4,61; 8,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,63; 12,06</t>
+          <t>7,67; 11,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,33; 8,91</t>
+          <t>5,32; 8,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,32; 62,88</t>
+          <t>8,38; 56,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,35; 7,66</t>
+          <t>5,33; 7,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,09; 10,89</t>
+          <t>8,04; 10,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,57; 7,83</t>
+          <t>5,53; 7,73</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,5; 42,88</t>
+          <t>10,47; 46,44</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,88; 9,17</t>
+          <t>3,93; 10,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,61; 9,31</t>
+          <t>4,99; 9,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,93; 7,8</t>
+          <t>3,86; 7,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,83; 21,05</t>
+          <t>14,09; 21,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,5; 10,0</t>
+          <t>5,46; 9,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,86; 13,47</t>
+          <t>8,86; 13,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,06; 10,34</t>
+          <t>6,2; 10,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,72; 15,31</t>
+          <t>9,4; 15,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,48; 8,99</t>
+          <t>5,36; 9,15</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,77; 11,18</t>
+          <t>7,94; 11,23</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,54; 8,41</t>
+          <t>5,51; 8,45</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,91; 16,71</t>
+          <t>11,83; 16,71</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,45</t>
+          <t>0,67; 4,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,63; 8,27</t>
+          <t>2,22; 8,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,84; 8,06</t>
+          <t>2,82; 8,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,2; 9,8</t>
+          <t>2,25; 10,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,18; 8,21</t>
+          <t>5,14; 7,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,39; 11,02</t>
+          <t>7,47; 11,08</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,17; 9,67</t>
+          <t>6,22; 9,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,43; 17,67</t>
+          <t>13,52; 17,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,63; 6,97</t>
+          <t>4,67; 6,97</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,88; 10,09</t>
+          <t>6,84; 9,83</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,91; 8,79</t>
+          <t>5,9; 8,89</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,09; 14,84</t>
+          <t>11,01; 14,81</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,29; 5,84</t>
+          <t>4,29; 5,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,49; 8,37</t>
+          <t>6,44; 8,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,8; 6,41</t>
+          <t>4,81; 6,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,21; 11,84</t>
+          <t>8,21; 11,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,5; 7,27</t>
+          <t>5,42; 7,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,14; 10,08</t>
+          <t>8,12; 10,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,99; 7,86</t>
+          <t>6,1; 7,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,48; 32,16</t>
+          <t>10,58; 31,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,06; 6,19</t>
+          <t>5,08; 6,23</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,62; 8,94</t>
+          <t>7,55; 8,94</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,71; 6,89</t>
+          <t>5,64; 6,87</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,32; 21,59</t>
+          <t>10,35; 22,47</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física</t>
+          <t>Hogares con personas con limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8870; 25337</t>
+          <t>9696; 26348</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11880; 34361</t>
+          <t>12532; 35792</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8812; 26450</t>
+          <t>8562; 25141</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34612; 61430</t>
+          <t>34708; 61951</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5609; 18200</t>
+          <t>5478; 18189</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11181; 28845</t>
+          <t>10869; 29248</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8597; 26429</t>
+          <t>8987; 26429</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18855; 35685</t>
+          <t>19974; 37111</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16440; 37124</t>
+          <t>17019; 38261</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27235; 54843</t>
+          <t>26516; 54170</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21810; 45793</t>
+          <t>21695; 44311</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>57855; 90684</t>
+          <t>57990; 89633</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4754; 18616</t>
+          <t>4867; 18889</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14034; 33794</t>
+          <t>15041; 34948</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10060; 26376</t>
+          <t>9826; 25953</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22196; 44449</t>
+          <t>21772; 43630</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9555; 26276</t>
+          <t>8478; 25394</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13091; 31883</t>
+          <t>12259; 30975</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6396; 22009</t>
+          <t>5736; 20807</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17630; 33216</t>
+          <t>18238; 33661</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17490; 38100</t>
+          <t>17161; 39624</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31331; 59104</t>
+          <t>30926; 57826</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19161; 42828</t>
+          <t>18564; 40972</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44662; 71618</t>
+          <t>45013; 72595</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>22338; 43249</t>
+          <t>21893; 44522</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>38128; 67876</t>
+          <t>38751; 70676</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23232; 46645</t>
+          <t>22124; 45569</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18523; 91628</t>
+          <t>20176; 91903</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7518; 22899</t>
+          <t>7513; 22630</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15011; 33129</t>
+          <t>14765; 34759</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7204; 24333</t>
+          <t>7226; 23758</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13559; 28207</t>
+          <t>13554; 29382</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>34487; 60192</t>
+          <t>33077; 60286</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59845; 96085</t>
+          <t>59896; 96306</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>34717; 61857</t>
+          <t>34723; 63208</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29358; 110346</t>
+          <t>29044; 108941</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62369; 97669</t>
+          <t>62747; 96658</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>85967; 130186</t>
+          <t>87434; 130156</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>56750; 94304</t>
+          <t>56151; 90610</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>108021; 150913</t>
+          <t>107231; 150457</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33979; 63920</t>
+          <t>32961; 61251</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>58480; 92460</t>
+          <t>58785; 91599</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44039; 73564</t>
+          <t>43925; 72910</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>81349; 615058</t>
+          <t>82005; 550714</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>104451; 149633</t>
+          <t>104011; 146590</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>155801; 209723</t>
+          <t>154842; 209123</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>110109; 154596</t>
+          <t>109274; 152747</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>211337; 863044</t>
+          <t>210822; 934845</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13614; 32161</t>
+          <t>13793; 35219</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>23527; 47550</t>
+          <t>25504; 48841</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24392; 48397</t>
+          <t>23950; 47848</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>65710; 100020</t>
+          <t>66951; 100937</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>31298; 56897</t>
+          <t>31036; 56528</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>67460; 102558</t>
+          <t>67509; 104850</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44772; 76323</t>
+          <t>45801; 76035</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>81810; 128782</t>
+          <t>79101; 129087</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>50354; 82671</t>
+          <t>49290; 84122</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>98887; 142238</t>
+          <t>101028; 142813</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>75244; 114300</t>
+          <t>74867; 114769</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>156773; 219994</t>
+          <t>155791; 219937</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2657; 13272</t>
+          <t>1988; 13235</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7018; 22084</t>
+          <t>5937; 22008</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8164; 23143</t>
+          <t>8099; 23572</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5292; 23575</t>
+          <t>5421; 25290</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>64677; 102497</t>
+          <t>64240; 99552</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>81935; 122198</t>
+          <t>82814; 122887</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>66797; 104647</t>
+          <t>67305; 104198</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>102260; 134521</t>
+          <t>102923; 134797</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>71599; 107838</t>
+          <t>72256; 107783</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>94696; 138892</t>
+          <t>94176; 135299</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>80975; 120333</t>
+          <t>80822; 121688</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>111067; 148664</t>
+          <t>110331; 148330</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>140338; 191001</t>
+          <t>140353; 188739</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>222171; 286352</t>
+          <t>220259; 288435</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>162492; 216872</t>
+          <t>162917; 216339</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>277017; 399573</t>
+          <t>277271; 400281</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>185848; 245617</t>
+          <t>183144; 241471</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>289043; 357987</t>
+          <t>288331; 359445</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>211641; 277644</t>
+          <t>215465; 278505</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>374886; 1150682</t>
+          <t>378579; 1140859</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>336574; 411677</t>
+          <t>337753; 413937</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>531612; 623567</t>
+          <t>526199; 623504</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>394680; 476333</t>
+          <t>390427; 475250</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>717501; 1501352</t>
+          <t>719801; 1562265</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_fisi_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_fisi_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 5,56</t>
+          <t>1,91; 5,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,87; 8,19</t>
+          <t>2,86; 7,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,86</t>
+          <t>2,23; 6,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,87; 12,26</t>
+          <t>6,55; 11,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 5,93</t>
+          <t>1,71; 6,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,46; 9,3</t>
+          <t>3,57; 9,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 7,62</t>
+          <t>2,74; 7,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,46; 8,29</t>
+          <t>4,25; 7,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,9</t>
+          <t>2,23; 4,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,53; 7,21</t>
+          <t>3,59; 7,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,71</t>
+          <t>2,79; 5,89</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,09; 9,41</t>
+          <t>5,87; 8,91</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 5,15</t>
+          <t>1,28; 5,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,59; 8,34</t>
+          <t>3,36; 8,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,6; 6,88</t>
+          <t>2,8; 7,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,81; 9,65</t>
+          <t>4,93; 9,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 6,83</t>
+          <t>2,59; 7,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,63; 9,16</t>
+          <t>3,61; 9,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 5,59</t>
+          <t>1,47; 5,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 8,8</t>
+          <t>4,8; 8,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,36</t>
+          <t>2,36; 5,46</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,09; 7,64</t>
+          <t>4,13; 7,76</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,47</t>
+          <t>2,57; 5,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,39; 8,7</t>
+          <t>5,36; 8,69</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 8,21</t>
+          <t>4,17; 8,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,16; 11,23</t>
+          <t>6,15; 10,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,24; 8,73</t>
+          <t>4,57; 8,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 13,75</t>
+          <t>9,53; 15,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,48; 13,49</t>
+          <t>4,6; 13,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,68; 13,36</t>
+          <t>5,97; 13,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,35; 14,3</t>
+          <t>4,39; 13,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,12; 17,6</t>
+          <t>8,19; 17,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,66; 8,49</t>
+          <t>4,74; 8,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,73; 10,83</t>
+          <t>6,65; 10,63</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,05; 9,19</t>
+          <t>5,09; 8,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,48; 13,04</t>
+          <t>9,81; 15,11</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,07; 7,81</t>
+          <t>5,04; 7,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,54; 11,23</t>
+          <t>7,58; 11,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,88; 7,88</t>
+          <t>4,94; 8,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,36; 14,54</t>
+          <t>10,33; 14,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,61; 8,58</t>
+          <t>5,01; 8,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,67; 11,95</t>
+          <t>7,64; 12,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,32; 8,83</t>
+          <t>5,33; 9,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,38; 56,3</t>
+          <t>7,66; 10,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,33; 7,51</t>
+          <t>5,39; 7,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,04; 10,86</t>
+          <t>8,03; 11,03</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,53; 7,73</t>
+          <t>5,51; 7,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,47; 46,44</t>
+          <t>9,62; 12,33</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,93; 10,05</t>
+          <t>3,99; 9,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,99; 9,57</t>
+          <t>5,06; 9,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,86; 7,71</t>
+          <t>3,89; 7,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,09; 21,25</t>
+          <t>12,25; 18,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,46; 9,94</t>
+          <t>5,35; 9,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,86; 13,77</t>
+          <t>8,83; 13,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,2; 10,3</t>
+          <t>6,12; 10,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,4; 15,34</t>
+          <t>13,33; 17,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,36; 9,15</t>
+          <t>5,42; 8,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,94; 11,23</t>
+          <t>7,89; 11,38</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,51; 8,45</t>
+          <t>5,62; 8,56</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,83; 16,71</t>
+          <t>13,46; 16,92</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,44</t>
+          <t>0,9; 4,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,22; 8,25</t>
+          <t>2,18; 7,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,82; 8,21</t>
+          <t>3,09; 8,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,25; 10,52</t>
+          <t>2,51; 10,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,14; 7,97</t>
+          <t>5,33; 7,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,47; 11,08</t>
+          <t>7,54; 11,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,22; 9,63</t>
+          <t>6,31; 9,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,52; 17,7</t>
+          <t>12,96; 17,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,67; 6,97</t>
+          <t>4,6; 6,94</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,84; 9,83</t>
+          <t>6,74; 9,71</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,9; 8,89</t>
+          <t>5,93; 8,82</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,01; 14,81</t>
+          <t>11,02; 14,88</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,29; 5,77</t>
+          <t>4,25; 5,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,44; 8,43</t>
+          <t>6,4; 8,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,81; 6,39</t>
+          <t>4,8; 6,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,21; 11,86</t>
+          <t>9,77; 11,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,42; 7,15</t>
+          <t>5,43; 7,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,12; 10,12</t>
+          <t>8,16; 10,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,1; 7,89</t>
+          <t>6,09; 7,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,58; 31,89</t>
+          <t>10,49; 12,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,08; 6,23</t>
+          <t>5,07; 6,23</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7,55; 8,94</t>
+          <t>7,62; 8,9</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,64; 6,87</t>
+          <t>5,64; 6,82</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,35; 22,47</t>
+          <t>10,42; 11,86</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45557</t>
+          <t>47362</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26331</t>
+          <t>28701</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>71888</t>
+          <t>76063</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9696; 26348</t>
+          <t>9059; 26360</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12532; 35792</t>
+          <t>12525; 33751</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8562; 25141</t>
+          <t>9573; 26786</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34708; 61951</t>
+          <t>36059; 63963</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5478; 18189</t>
+          <t>5243; 18553</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10869; 29248</t>
+          <t>11224; 29965</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8987; 26429</t>
+          <t>9515; 26804</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19974; 37111</t>
+          <t>20746; 38465</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17019; 38261</t>
+          <t>17367; 36864</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26516; 54170</t>
+          <t>26988; 54414</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21695; 44311</t>
+          <t>21640; 45722</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>57990; 89633</t>
+          <t>61006; 92551</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31916</t>
+          <t>33772</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24851</t>
+          <t>28051</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>56767</t>
+          <t>61824</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4867; 18889</t>
+          <t>4691; 19055</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15041; 34948</t>
+          <t>14065; 34344</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9826; 25953</t>
+          <t>10577; 26780</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21772; 43630</t>
+          <t>23804; 47353</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8478; 25394</t>
+          <t>9644; 26713</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12259; 30975</t>
+          <t>12204; 31747</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5736; 20807</t>
+          <t>5467; 21374</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18238; 33661</t>
+          <t>20308; 37498</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17161; 39624</t>
+          <t>17450; 40349</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30926; 57826</t>
+          <t>31269; 58758</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18564; 40972</t>
+          <t>19259; 41933</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>45013; 72595</t>
+          <t>48596; 78762</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53832</t>
+          <t>57259</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19767</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>73599</t>
+          <t>79723</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>21893; 44522</t>
+          <t>22601; 43968</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>38751; 70676</t>
+          <t>38735; 69162</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22124; 45569</t>
+          <t>23869; 45800</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20176; 91903</t>
+          <t>44937; 71947</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7513; 22630</t>
+          <t>7717; 21870</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14765; 34759</t>
+          <t>15540; 34142</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7226; 23758</t>
+          <t>7289; 23003</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13554; 29382</t>
+          <t>15353; 33066</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>33077; 60286</t>
+          <t>33645; 59708</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59896; 96306</t>
+          <t>59172; 94544</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>34723; 63208</t>
+          <t>35055; 61562</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29044; 108941</t>
+          <t>64633; 99591</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>127917</t>
+          <t>138618</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>273853</t>
+          <t>79216</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>401770</t>
+          <t>217834</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62747; 96658</t>
+          <t>62426; 95510</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>87434; 130156</t>
+          <t>87875; 128744</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>56151; 90610</t>
+          <t>56808; 92409</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>107231; 150457</t>
+          <t>116883; 159891</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32961; 61251</t>
+          <t>35761; 62608</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>58785; 91599</t>
+          <t>58551; 92958</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43925; 72910</t>
+          <t>44029; 75115</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>82005; 550714</t>
+          <t>65961; 93723</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>104011; 146590</t>
+          <t>105236; 148869</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>154842; 209123</t>
+          <t>154587; 212422</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>109274; 152747</t>
+          <t>108858; 153905</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>210822; 934845</t>
+          <t>191789; 245720</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82188</t>
+          <t>85679</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>109220</t>
+          <t>125041</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>191408</t>
+          <t>210720</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13793; 35219</t>
+          <t>13970; 33846</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25504; 48841</t>
+          <t>25815; 48434</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23950; 47848</t>
+          <t>24145; 48953</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>66951; 100937</t>
+          <t>69600; 106230</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>31036; 56528</t>
+          <t>30431; 55162</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>67509; 104850</t>
+          <t>67274; 103888</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45801; 76035</t>
+          <t>45151; 77223</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>79101; 129087</t>
+          <t>110787; 142452</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>49290; 84122</t>
+          <t>49815; 82190</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>101028; 142813</t>
+          <t>100351; 144720</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>74867; 114769</t>
+          <t>76351; 116341</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>155791; 219937</t>
+          <t>188348; 236650</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12007</t>
+          <t>11944</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>117738</t>
+          <t>127029</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>129745</t>
+          <t>138973</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1988; 13235</t>
+          <t>2677; 14583</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5937; 22008</t>
+          <t>5828; 21051</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8099; 23572</t>
+          <t>8862; 23345</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5421; 25290</t>
+          <t>5943; 24978</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>64240; 99552</t>
+          <t>66529; 99455</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>82814; 122887</t>
+          <t>83630; 122050</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>67305; 104198</t>
+          <t>68309; 105329</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>102923; 134797</t>
+          <t>109418; 145616</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>72256; 107783</t>
+          <t>71205; 107426</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>94176; 135299</t>
+          <t>92804; 133700</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>80822; 121688</t>
+          <t>81168; 120704</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>110331; 148330</t>
+          <t>119186; 160927</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>353417</t>
+          <t>374634</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>571760</t>
+          <t>410503</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>925176</t>
+          <t>785137</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>140353; 188739</t>
+          <t>138866; 187347</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>220259; 288435</t>
+          <t>219046; 282462</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>162917; 216339</t>
+          <t>162590; 215214</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>277271; 400281</t>
+          <t>336489; 410672</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>183144; 241471</t>
+          <t>183566; 242323</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>288331; 359445</t>
+          <t>289643; 360784</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>215465; 278505</t>
+          <t>215057; 279164</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>378579; 1140859</t>
+          <t>381446; 442338</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>337753; 413937</t>
+          <t>337279; 414241</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>526199; 623504</t>
+          <t>531077; 620498</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>390427; 475250</t>
+          <t>390109; 471588</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>719801; 1562265</t>
+          <t>737763; 839328</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_fisi_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_fisi_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad física (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
